--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="投递总表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计看板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="投递总表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="统计看板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,10 +33,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
       <sz val="14"/>
     </font>
     <font>
@@ -47,7 +43,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -58,36 +54,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="002F5496"/>
         <bgColor rgb="002F5496"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002196F3"/>
-        <bgColor rgb="002196F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9800"/>
-        <bgColor rgb="00FF9800"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009C27B0"/>
-        <bgColor rgb="009C27B0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F44336"/>
-        <bgColor rgb="00F44336"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009E9E9E"/>
-        <bgColor rgb="009E9E9E"/>
       </patternFill>
     </fill>
   </fills>
@@ -109,32 +75,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -500,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -573,245 +521,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>拼多多</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>合规策略管培生</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>官网</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>已投递</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>等笔试通知</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.pddglobalhr.com/campus/grad</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-02 23:52</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>京东</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>TET-产品方向</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>内推</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>笔试</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>收到笔试通知7月10日考</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>复习行测+专业知识</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>https://campus.jd.com/#/jobs</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-02 23:52</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>小红书</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>产品工程师-商业技术</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>官网</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>一面</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>一面定在7月8日下午2点</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>准备项目介绍+产品分析</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>https://job.xiaohongshu.com/campus/position</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-02 23:52</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>美团</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>产品管培生</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>内推</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>已拒</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>感谢信，岗位不匹配</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>https://zhaopin.meituan.com</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-02 23:52</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>字节跳动</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>内容运营</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>牛客</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>待投递</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>先刷笔试题再投</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-02 23:52</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -823,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -832,7 +541,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>投递统计看板</t>
         </is>
@@ -841,232 +550,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-02 23:52</t>
+          <t>更新时间: 2026-07-02 23:54</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>总投递数: 5</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>总投递数: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>按状态分布</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>占比</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>一面</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>已投递</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-    </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>已拒</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>20.0%</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>按渠道分布</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>待投递</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>笔试</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>20.0%</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>渠道</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>投递公司一览</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>按渠道分布</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>渠道</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>内推</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>官网</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>牛客</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>投递公司一览</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>公司</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>投递数</t>
         </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>美团</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>拼多多</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>小红书</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>字节跳动</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>京东</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-02 23:54</t>
+          <t>更新时间: 2026-07-03 00:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-03 00:05</t>
+          <t>更新时间: 2026-07-03 12:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-03 12:36</t>
+          <t>更新时间: 2026-07-04 12:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-04 12:29</t>
+          <t>更新时间: 2026-07-05 12:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-05 12:51</t>
+          <t>更新时间: 2026-07-06 13:04</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-06 13:04</t>
+          <t>更新时间: 2026-07-07 12:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-07 12:43</t>
+          <t>更新时间: 2026-07-08 12:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-08 12:10</t>
+          <t>更新时间: 2026-07-09 12:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-09 12:48</t>
+          <t>更新时间: 2026-07-10 12:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-10 12:44</t>
+          <t>更新时间: 2026-07-11 12:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-11 12:07</t>
+          <t>更新时间: 2026-07-12 12:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-12 12:21</t>
+          <t>更新时间: 2026-07-13 12:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-13 12:25</t>
+          <t>更新时间: 2026-07-14 11:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-14 11:52</t>
+          <t>更新时间: 2026-07-15 11:53</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-15 11:53</t>
+          <t>更新时间: 2026-07-16 11:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-16 11:57</t>
+          <t>更新时间: 2026-07-17 11:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-17 11:55</t>
+          <t>更新时间: 2026-07-18 11:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-18 11:49</t>
+          <t>更新时间: 2026-07-19 12:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-19 12:17</t>
+          <t>更新时间: 2026-07-20 12:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-20 12:31</t>
+          <t>更新时间: 2026-07-21 12:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-21 12:10</t>
+          <t>更新时间: 2026-07-22 12:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-22 12:12</t>
+          <t>更新时间: 2026-07-23 12:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-23 12:10</t>
+          <t>更新时间: 2026-07-24 12:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-24 12:08</t>
+          <t>更新时间: 2026-07-25 11:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-25 11:58</t>
+          <t>更新时间: 2026-07-26 12:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-26 12:22</t>
+          <t>更新时间: 2026-07-27 12:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-27 12:31</t>
+          <t>更新时间: 2026-07-28 11:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-28 11:55</t>
+          <t>更新时间: 2026-07-29 11:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-29 11:58</t>
+          <t>更新时间: 2026-07-30 11:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-30 11:51</t>
+          <t>更新时间: 2026-07-31 12:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-07-31 12:17</t>
+          <t>更新时间: 2026-08-01 12:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-01 12:16</t>
+          <t>更新时间: 2026-08-02 12:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-02 12:19</t>
+          <t>更新时间: 2026-08-03 12:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-03 12:24</t>
+          <t>更新时间: 2026-08-04 11:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-04 11:59</t>
+          <t>更新时间: 2026-08-05 11:56</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-05 11:56</t>
+          <t>更新时间: 2026-08-05 14:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-05 14:12</t>
+          <t>更新时间: 2026-08-05 16:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-05 16:16</t>
+          <t>更新时间: 2026-08-06 09:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-06 09:43</t>
+          <t>更新时间: 2026-08-06 12:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-06 12:09</t>
+          <t>更新时间: 2026-08-07 11:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-07 11:47</t>
+          <t>更新时间: 2026-08-08 10:53</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-08 10:53</t>
+          <t>更新时间: 2026-08-09 11:00</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-09 11:00</t>
+          <t>更新时间: 2026-08-10 11:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-10 11:09</t>
+          <t>更新时间: 2026-08-11 11:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-11 11:02</t>
+          <t>更新时间: 2026-08-12 11:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-12 11:21</t>
+          <t>更新时间: 2026-08-13 11:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-13 11:24</t>
+          <t>更新时间: 2026-08-14 11:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-14 11:22</t>
+          <t>更新时间: 2026-08-15 10:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-15 10:12</t>
+          <t>更新时间: 2026-08-16 10:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-16 10:19</t>
+          <t>更新时间: 2026-08-17 10:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-17 10:18</t>
+          <t>更新时间: 2026-08-18 10:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-18 10:14</t>
+          <t>更新时间: 2026-08-19 10:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-19 10:16</t>
+          <t>更新时间: 2026-08-20 10:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-20 10:15</t>
+          <t>更新时间: 2026-08-21 10:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-21 10:22</t>
+          <t>更新时间: 2026-08-22 10:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-22 10:14</t>
+          <t>更新时间: 2026-08-23 10:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-23 10:22</t>
+          <t>更新时间: 2026-08-24 10:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-24 10:21</t>
+          <t>更新时间: 2026-08-25 10:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-25 10:16</t>
+          <t>更新时间: 2026-08-26 10:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-26 10:23</t>
+          <t>更新时间: 2026-08-27 18:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-27 18:52</t>
+          <t>更新时间: 2026-08-28 20:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-28 20:27</t>
+          <t>更新时间: 2026-08-29 15:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 15:37</t>
+          <t>更新时间: 2026-08-30 14:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 14:11</t>
+          <t>更新时间: 2026-08-31 14:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 14:36</t>
+          <t>更新时间: 2026-09-01 13:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 13:59</t>
+          <t>更新时间: 2026-09-02 13:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 13:24</t>
+          <t>更新时间: 2026-09-03 13:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 13:26</t>
+          <t>更新时间: 2026-09-04 13:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 13:25</t>
+          <t>更新时间: 2026-09-05 13:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 13:13</t>
+          <t>更新时间: 2026-09-06 13:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 13:28</t>
+          <t>更新时间: 2026-09-07 13:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 13:38</t>
+          <t>更新时间: 2026-09-08 13:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 13:34</t>
+          <t>更新时间: 2026-09-09 13:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 13:41</t>
+          <t>更新时间: 2026-09-10 13:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 13:32</t>
+          <t>更新时间: 2026-09-11 13:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 13:35</t>
+          <t>更新时间: 2026-09-12 13:21</t>
         </is>
       </c>
     </row>
